--- a/plans/backlog.xlsx
+++ b/plans/backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lzx_8\Desktop\eggitor\1_开发中\大富翁\monopoly\plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9744E6C-C114-4986-9291-C901B4150D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A115C95F-F14E-40B2-A421-F80BA2EE851A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,32 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>玩家移动</t>
+  </si>
+  <si>
+    <t>载具移动</t>
+  </si>
+  <si>
+    <t>回合事件</t>
+  </si>
+  <si>
+    <t>3c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ui </t>
+  </si>
+  <si>
+    <t>init</t>
+  </si>
+  <si>
+    <t>场景引用</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -337,9 +363,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="D3:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>